--- a/光伏配储项目/电价数据/2026/布基站.xlsx
+++ b/光伏配储项目/电价数据/2026/布基站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.5099900000000001</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38074</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.85763</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.6362599999999999</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.6510499999999999</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.52524</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.50445</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.43748</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.4543</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.43852</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42298</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.41904</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.40871</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.39795</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.39958</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.38483</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40191</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.423</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41246</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35442</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.3914</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.38489</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.41685</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39205</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.42062</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.41382</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.42381</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41278</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44376</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.35662</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30004</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.33189</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.25425</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.29513</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.30339</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.30576</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.31643</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.12153</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.09878000000000001</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.10981</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.09636</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.12077</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.22573</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.35205</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.41137</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.32807</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.08131000000000001</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.09048</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.27027</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.13665</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.30903</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.28015</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.8125599999999999</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.6011599999999999</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.22396</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.23725</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.07912999999999999</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.52054</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.51485</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.76252</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.27394</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.9263899999999999</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.78599</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.19421</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.9344600000000001</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>1.00103</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.45157</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.5239199999999999</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.5086</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.49936</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>0.76503</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.68275</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.6149600000000001</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.41842</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.57404</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.46188</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>0.6182300000000001</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>0.80962</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>0.6633300000000001</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.62706</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>0.76212</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>0.99678</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.5066499999999999</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.6754</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.5694199999999999</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>0.73766</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.56126</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.54688</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.6416000000000001</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.61383</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.47301</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.47578</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.39968</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41599</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42565</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32917</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.69765</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.3763</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.7289800000000001</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.18389</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.7703099999999999</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.5230900000000001</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.5188400000000001</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.50518</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.50881</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.4894</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.40138</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.4699700000000001</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.37977</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.38003</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39129</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33685</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.37031</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35575</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.35872</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.3752200000000001</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.37513</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.35918</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.38006</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.41929</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.50005</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.59309</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.66865</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.43008</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.36557</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.41256</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34765</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.33597</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.42076</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.51425</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.43421</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.29707</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.40927</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.0562</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>1.04132</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>1.07728</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>1.04206</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>1.0026</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.9175</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.79283</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.62737</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.7095900000000001</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>1.628</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.3362</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.39599</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.41793</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.42963</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>1.4157</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.49988</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.37225</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.12961</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.28409</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.99909</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.9272899999999999</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.34193</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.32077</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.49411</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.33782</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.39602</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>1.22801</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>1.02558</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.80521</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>0.8322000000000001</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>0.38182</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>0.42462</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>0.29365</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.40777</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>0.35748</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>0.5737000000000001</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>0.6987599999999999</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>0.56657</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>0.6926</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.7417</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.7279500000000001</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.56387</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.52037</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.73887</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0.52779</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>1.03012</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.2319</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.82367</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>1.08332</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.9125</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.59714</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.589</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.76658</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.87407</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.46681</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.42048</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33456</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32146</v>
+      </c>
+      <c r="C119" t="n">
+        <v>1.16431</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.44067</v>
+      </c>
+      <c r="E119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.47575</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.51493</v>
+      </c>
+      <c r="I119" t="n">
+        <v>1.27161</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.39002</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.49236</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.44167</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.58897</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.6240599999999999</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.38261</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37074</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39614</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.45063</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.44691</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35579</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.36128</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.3516</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36678</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35901</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.38464</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39646</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47386</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.61821</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.6117</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.40704</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.50839</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35299</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.4456</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.4029</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.35836</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.20615</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.26703</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.34674</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.34108</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.36502</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.369</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.34277</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.47493</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.51405</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.52181</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.32548</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.48537</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.41255</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.29591</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.16084</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.31456</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.27024</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.31691</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.29771</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.28294</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.29374</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.33913</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.30046</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.28226</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.38768</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.39328</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.35529</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.41541</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.48931</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.34742</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.42714</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>0.41631</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.37863</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.3911</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.34344</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.36048</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.53784</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.61788</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.62181</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.86441</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.33091</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.47361</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.47253</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.49768</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.41141</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.44972</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.44192</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.46235</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.44856</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.40249</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.37882</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.42636</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.40518</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.39911</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.40301</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36536</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.3491</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34238</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31922</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.39793</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.40158</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.31951</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.37676</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.37302</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.37307</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.34997</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.34261</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.36567</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.34731</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.34062</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.45708</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.34281</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.33359</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.34094</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.34291</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.34283</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.31816</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.3201</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.31759</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.31398</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.3176</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.34017</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33923</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35372</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.36916</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.38934</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.34393</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.35733</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.32822</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.36367</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.38005</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.3855</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.31577</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.60663</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.53171</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.2362</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.22378</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.58172</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>1.08628</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>1.04767</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>1.51496</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.33312</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.6696</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>1.01701</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>1.30574</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>1.01652</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.34513</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.07776000000000001</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.84194</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>1.01029</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.31179</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.57463</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.5969500000000001</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>1.70504</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.06492000000000001</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.4564</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.31517</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.2689</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.40365</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.36418</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.33588</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.24414</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.25656</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.23205</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.29319</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.14365</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.29673</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.29354</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.3088399999999999</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.33619</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.32088</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.33801</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.35866</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.34322</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.38349</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.4221</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.5746599999999999</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.46758</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.4626</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.38496</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.36625</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.37086</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.38255</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.50225</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.5598500000000001</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.64001</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.57374</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.44869</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.35802</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.34513</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.53761</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.32108</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.31385</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.29867</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.32762</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.45576</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.38235</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.37281</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.33889</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.3013</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.32395</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.40005</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.31103</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.30961</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.29805</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.30587</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.31131</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.29866</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.3034</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.29024</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.29025</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.29031</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.29808</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.2922</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.29519</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31235</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.30829</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31647</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.3245</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32436</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33271</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32614</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.27944</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.26067</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.42821</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.04634000000000001</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.41343</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.48613</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.0445</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.0483</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.23178</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.04873</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>-0.03321</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>-0.04686999999999999</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>-0.04509000000000001</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>-0.04099</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>-0.03934</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>-0.03965</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>-0.04043</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>-0.04021</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>-0.03828</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.04133</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>-0.04479</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>-0.04131</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>-0.04076</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.04158</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.04224</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>-0.04591</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>-0.04169</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>-0.04592</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.21886</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.04826</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.05461999999999999</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.05656</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>0.02038</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.09834</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.54491</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.4845</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.45837</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.29016</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.33163</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.29385</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31996</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32956</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31532</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.3354</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33511</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33535</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.33398</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.38655</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.39213</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.38751</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.36794</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.34137</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.38992</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39994</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.39329</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46765</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.35468</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39654</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.40015</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.41728</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35505</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35811</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.33986</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.36114</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.35104</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.36802</v>
+      </c>
+      <c r="C122" t="n">
+        <v>1.12428</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.40048</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.44685</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.42388</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.42396</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.36002</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.35921</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.36857</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.33347</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.30935</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.32454</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.38968</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.35541</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.34759</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.34625</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.33512</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.31556</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.3303</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.33566</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.32277</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.30026</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.32284</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33542</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.3391</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.35029</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.35211</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.34292</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.31618</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10253</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04353</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04689</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04549</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04609000000000001</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04609000000000001</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04609000000000001</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04543999999999999</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04379</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>-0.03383</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>-0.04248</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.10586</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>-0.00061</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.03897999999999999</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>-0.04745000000000001</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.04274</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04368</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04372</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04559000000000001</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.04546</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04543</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04344</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04309</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04532</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04316</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.04118</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.045</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04512</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04523</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.0434</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04404</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>-0.04081</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>-0.04276</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04451</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04995</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04971</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.04727000000000001</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04765999999999999</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.20009</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14297</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.29029</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29499</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30487</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.30017</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29527</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29316</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29374</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.2927</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29715</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29107</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29525</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26907</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29412</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29834</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30875</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30413</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30232</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31467</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31871</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34789</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.34986</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34476</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.36675</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36524</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33574</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33065</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.3179</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31068</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.40489</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.35022</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32091</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30745</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31489</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30161</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28139</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29468</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29101</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28827</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28115</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27141</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.2712</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.28129</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17257</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.15882</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17114</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14788</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15961</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15878</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23645</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.2142</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22674</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26909</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28597</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.291</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31959</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.29101</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28115</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.28128</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28074</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27131</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28117</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32269</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31048</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30524</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.31658</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30963</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35924</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31624</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29544</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.38296</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.38013</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.42773</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.45425</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41777</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41463</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.38916</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40193</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30008</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.301</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29935</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15649</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29402</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.3108399999999999</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31329</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31281</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32188</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34605</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30073</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33091</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38532</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.50769</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79096</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.62205</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40005</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.498</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.78104</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92043</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49459</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.91601</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.86809</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.29922</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.359</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.89283</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.63258</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.19234</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.87139</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.5464600000000001</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.3362</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.03661</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.53612</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.79548</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.5308200000000001</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.77751</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.78113</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8773300000000001</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.8762300000000001</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49737</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.40281</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.40535</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.45478</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.21245</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87903</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55114</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62727</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.5396799999999999</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49927</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45651</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42492</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43813</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.45022</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38956</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45278</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.42014</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.35263</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.40005</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.3653</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38649</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41488</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43391</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34395</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.3904</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.35071</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.34333</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.33701</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.34798</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.40439</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.35028</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.45086</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.35449</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.40035</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.40032</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.58701</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.42813</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.5961799999999999</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.60262</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.67379</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.47032</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.4186</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.58068</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.4519</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.88126</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.63518</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>1.28059</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.26233</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.86312</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.34632</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.44248</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.33071</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.33407</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.30621</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>1.09692</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>1.43111</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.29814</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.9286</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.32278</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.35736</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.33287</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32095</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.33692</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.33766</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31799</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.30631</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31917</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.31988</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.34409</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.31504</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.31519</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.3202</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29936</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.31223</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.31381</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.31225</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.31559</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.31029</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.31549</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.3226</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.32375</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.32503</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.35464</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.34101</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.34038</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.33827</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.33063</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.33758</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.33557</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.41043</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.41307</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.4529</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.41543</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.39187</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.37533</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.35354</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32856</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.92649</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.36068</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.46802</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.36978</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.42458</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.48248</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.38355</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.41019</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.36758</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.37633</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.35656</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.34901</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.38937</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.33073</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35938</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.34586</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32305</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.40051</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.50069</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.35731</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.38799</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.34367</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.35105</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.35547</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.37092</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.35814</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.36326</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31665</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.3137200000000001</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33279</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.33833</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.34475</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.35537</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.31499</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.3132200000000001</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.29076</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.31313</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.28981</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.34644</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.16517</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.31224</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.31118</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.37288</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.31066</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.32659</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.29731</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.26228</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.19918</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.27726</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.20056</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.31399</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.27808</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.31152</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.3156</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.38817</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.36836</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.31732</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.31473</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.32446</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.30755</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.31658</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.29438</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.3158</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.29025</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.31069</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.32911</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.31834</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.29007</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.35104</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.25568</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.3502</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.32216</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.30313</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.34298</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.27639</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.35347</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.3292</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.34078</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.31016</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.35049</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.32693</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.38595</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.34091</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.43795</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.35025</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.33003</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.42323</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.35177</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44895</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.32834</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.42075</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35908</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40205</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.40079</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.59777</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.35051</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.89061</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.48478</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.26538</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.7496900000000001</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.85751</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.7012999999999999</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.62041</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.47114</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.46896</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.52764</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.45845</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.45586</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.43006</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.42763</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.43991</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.5281699999999999</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.42763</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.4518</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.42648</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.45469</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.40191</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.44522</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.47085</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.40866</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.4397</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.45219</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.42763</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.42761</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.41343</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.44011</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.48706</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.42308</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.52566</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.37702</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.38351</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.29698</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.43189</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.43418</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.31458</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.37788</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.31089</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>1.288</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.3097200000000001</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.86617</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>1.31055</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.26429</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>1.17672</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>1.1459</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>1.40191</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30629</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.26356</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.26004</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.31197</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.28892</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.29262</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.49282</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.29575</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.3238</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.31569</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.33475</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.35776</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.31941</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.34489</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.34519</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.41842</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.41346</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.35562</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.36625</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.34175</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.33617</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.37305</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.36013</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.36314</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.37174</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.36286</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.34977</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.57782</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.47951</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.85178</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.48744</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.43766</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.37544</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.42303</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.38607</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.36901</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.33386</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.34058</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.32899</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.32427</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.31849</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.43491</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.33914</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.3460299999999999</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.3397</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.33605</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.32585</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.3291</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.32591</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.32461</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.32393</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.30964</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.32702</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.32562</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.31926</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.31533</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.32155</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.3201</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.30973</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.32678</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.31085</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.31987</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.32043</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.40311</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.32563</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.35411</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.40845</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.38138</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.35527</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.33953</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.36111</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.33495</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.33903</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.32025</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.29685</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.37765</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>1.29087</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>1.21858</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>1.22697</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>1.16582</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.9468799999999999</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.6080099999999999</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.62387</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.7699199999999999</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.6126699999999999</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.30943</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.59104</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.30918</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.5798</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.88378</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.5384500000000001</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.9103300000000001</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>1.06901</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.5351900000000001</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>1.41031</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.47615</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.58123</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>1.54569</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.59221</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.60605</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>1.14886</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.79975</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.8091499999999999</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.80265</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.8241000000000001</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.43125</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.9064800000000001</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.88888</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>1.61093</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.35517</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.38966</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.35193</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.41103</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.36771</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.39256</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.46391</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.40687</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.40146</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.40896</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.40411</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.45944</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.45391</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.45312</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.45875</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.45864</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.41113</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.39741</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.40418</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.39721</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.36086</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.36296</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.34784</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.34903</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.33931</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.56933</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.39852</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.49114</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.43979</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.43077</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.37737</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.39367</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.38966</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.4046</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.38954</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.37847</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.39043</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.36733</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.40284</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.37896</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.39047</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.35601</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.35262</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.36029</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.34984</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.3445299999999999</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.35027</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.34454</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.34986</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.36211</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.39045</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.36734</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.3445</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.34475</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.34469</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.33073</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.3496</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.3573</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.37467</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.29746</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.31567</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31509</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.31584</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.30085</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.28181</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.2746</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.26399</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.1979</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.30662</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.24803</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.2407</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.26802</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30676</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.29162</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31649</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.3001</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.29164</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.26983</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.30556</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.29187</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.2763</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.2401</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.31043</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.31504</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.29579</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.3033</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.28349</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.31759</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.33987</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.34233</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.3456</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.33222</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.33104</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.33368</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.34799</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.35887</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.35226</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.3651</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.37796</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.84874</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.95329</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.6214500000000001</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.50282</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.6708099999999999</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.38735</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.35991</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.35757</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.35732</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.42551</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.34058</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.34371</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.37112</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.36773</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.36159</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.38615</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.38633</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.39183</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.34992</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.36458</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.3400899999999999</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36238</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.40215</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.37208</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.38858</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.37663</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.35408</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.34939</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.35823</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.35468</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.34176</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.35011</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.34783</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.3511</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.34022</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.35112</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.3419</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.34358</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.34458</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.33952</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.33932</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.33424</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.33054</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.33501</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.33239</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.34991</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.34441</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.36174</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.31336</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.33122</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.33929</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.32608</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.32252</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.33571</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.336</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>1.33601</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.53001</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.3737</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.35095</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.40353</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.4303</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.32954</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.54367</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.30926</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.29896</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.37082</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.40873</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.29914</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.25044</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.90515</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.50842</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.22521</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.29769</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.2975</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.32575</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.29992</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.28169</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.30584</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.31815</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.31493</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.29805</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.32671</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.35974</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.36239</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.34217</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.59787</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.3519</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.35097</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.35971</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.36951</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.32181</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.39258</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.32407</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.33206</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.33685</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.34626</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.34224</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.45894</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.37631</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.70239</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.36896</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.3909</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.33428</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.32251</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.32311</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.5022300000000001</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.25958</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.38631</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.30644</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.3177</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.32964</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.32838</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.30903</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.30446</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.2884</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32307</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.30502</v>
+      </c>
+      <c r="D130" t="n">
+        <v>1.09652</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.34556</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.33164</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.32524</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.33045</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.32571</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.32575</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.31922</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.32385</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.32605</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.32415</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.32717</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.32836</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.32695</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.32747</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.32409</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.33116</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.32631</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.32085</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.31989</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.32309</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.3265</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.33087</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.33961</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.34086</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.34098</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.33261</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.33999</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.32137</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.32121</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.33496</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.35201</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.353</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.33546</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.3251</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.32139</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.32187</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.32469</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.31758</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.34094</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.30064</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.33844</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.34439</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.31276</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.32554</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.28091</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.32566</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.31888</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.32187</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.3262</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32872</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.33444</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.34325</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.30513</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.33431</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.32565</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.32053</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.32204</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.31446</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.3506</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.31142</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.30993</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.32674</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.36595</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.34478</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.34566</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.33476</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.35012</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.35015</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.35017</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.3608</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.33272</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.33068</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.34884</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.38232</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.37235</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.36481</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.37211</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.36593</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.37822</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.36359</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.39929</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.38734</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.3733399999999999</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.41393</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.35576</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.36982</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.36232</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.3614</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.35062</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.3501</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.34262</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34964</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.3355</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.34493</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.34509</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.3516</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.34557</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.3509</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.3501</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.34401</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34389</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.34118</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.35356</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.34186</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.34508</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.3440299999999999</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33716</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.33546</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.3401</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.33554</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.3611</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32444</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.33443</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.33546</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.3440299999999999</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.33558</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.3451</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.33234</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.34401</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.34401</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33267</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.34166</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.3258</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.34486</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.34903</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.33652</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.34133</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.31289</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.33123</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.33503</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.33653</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.33193</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.32334</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.33288</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.32364</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.32358</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.33474</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.3278</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.33279</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.32433</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.38383</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32313</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.32242</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.3204</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.31678</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.32268</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.33082</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.32916</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32225</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.32346</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.33036</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.33076</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.33252</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.33836</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.34739</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.36325</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.38793</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.36076</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.35755</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.35841</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.37176</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.35294</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.36405</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34855</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.36348</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.36198</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36431</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.35052</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.38594</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.37939</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.38323</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.38463</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.42358</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.4169</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.37115</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.37954</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.65383</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.8428600000000001</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.4426</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.30004</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.47031</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.39223</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.3447</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.34475</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.3523</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.3355</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.33969</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.3097</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.40533</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.37541</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.37103</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.36217</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.35928</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.35899</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.36214</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.35141</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.36047</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.35911</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35299</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.36011</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.36049</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35348</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35214</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.35942</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.36094</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.36126</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.33725</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.37223</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.3588</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35743</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.36009</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.36009</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.36935</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36671</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.37962</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35889</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.3565</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.35416</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35494</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35396</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.34568</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.32956</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.32615</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.3391</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.3322</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.26463</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.14333</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.30303</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.28578</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.28444</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.19971</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.25996</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.2801</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.32609</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.28001</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.22091</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.26935</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.28592</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.27939</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.28992</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.29288</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.30557</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.33879</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.3232</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.14781</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.29267</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.29762</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.35445</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.32915</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.34862</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.3384</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.34604</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.35725</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.32799</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.30757</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.3298</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.35403</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.33749</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.36347</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.32123</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.36238</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.43695</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.3874</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.5207999999999999</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.82859</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.5807599999999999</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.9903</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.6850000000000001</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.6944</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.8118500000000001</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.9285099999999999</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.44882</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.4762</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.40973</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.37889</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.3644</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.47858</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.43068</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.41092</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.37742</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.37483</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.36732</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.36017</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34389</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.49032</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.51337</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.46943</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.47473</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.42035</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.39385</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.40467</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.41174</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.4164</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.42466</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.40727</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.39954</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.41706</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.42019</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.40232</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.39609</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.43169</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.3962</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.42488</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.39896</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.4064700000000001</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.40642</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.42083</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.40131</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.46813</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.45708</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.58733</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.52561</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.46835</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.33403</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.44136</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.49701</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.37388</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.38833</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.47317</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.512</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.48498</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.61221</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.42565</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.30096</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.33525</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.37612</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.48946</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.43651</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.43018</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.32867</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.3729</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.28953</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.33522</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.33158</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.34404</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.34811</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.37138</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.6438700000000001</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.37034</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.34428</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.16884</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.29189</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.39045</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.40172</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.32532</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.34388</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.38726</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.34111</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.38142</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.37024</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.37931</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.35547</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.3604</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.35445</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.39363</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.33924</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.42786</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.44786</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.51206</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.45046</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.53772</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.49725</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.80468</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.85803</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.6822699999999999</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.72923</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.80838</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.5748099999999999</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.50531</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.77071</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.7152000000000001</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.62046</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.64938</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.43651</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.47528</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.46746</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.47798</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.45457</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.41808</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.54623</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.42945</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.4418</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.44828</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.42112</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.41959</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.43961</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.40534</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.39947</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.44631</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.3982</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.40435</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.38888</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.38682</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.3785</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.37357</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35688</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36586</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.37686</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.37127</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.36021</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.35696</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36586</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.37987</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.39031</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.37383</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.36265</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.35827</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35293</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.37386</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.40042</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.37726</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.38717</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.40973</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.39323</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.38436</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35336</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.37291</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.34526</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.34067</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.35431</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.38515</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.22978</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.39383</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.34462</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.35043</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.36612</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.35101</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.4056</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.35775</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.47883</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.41034</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.46522</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.33417</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.31888</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.11434</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.18125</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.30103</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.29606</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.32129</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.35366</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.35291</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.34896</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.35118</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.37427</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.38028</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.37549</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.42859</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.4166</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.36995</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.4178</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.41417</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.38804</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.37839</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.38534</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.39085</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.40929</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.40831</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.34574</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.36963</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.3766600000000001</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.38913</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.37384</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35508</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.39846</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.38056</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.37512</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.35742</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.39575</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.38084</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36583</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.33011</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.44536</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.36127</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.39576</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.39545</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.35737</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.37918</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.3506</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.37893</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.35765</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.35896</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.35568</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.35054</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.35953</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.34649</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.35126</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.34949</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.34041</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.33149</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.3401</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.3404</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.33549</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.3405</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.34551</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.33094</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.33051</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.33126</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.33134</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.33823</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.31946</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.31061</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.30523</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.31814</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.27539</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.32051</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.31527</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.30976</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.22819</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.28824</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.23043</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.28988</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.25027</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.25952</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.14027</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.29422</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.29961</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.32319</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.25215</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04337</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.25134</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.29481</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.16972</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.18292</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.28052</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.3104</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.31836</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.22906</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.25043</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.26479</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.23258</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.27562</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.28454</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.28338</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.32775</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.32841</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.30789</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.35336</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.34912</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.35385</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.36055</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.35438</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.35794</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.3313</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.37479</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.36141</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.34454</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.3105</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.35793</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.35848</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.38158</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.35577</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.37052</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.37062</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.37156</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.3454100000000001</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.3652</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.38041</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.34123</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.36391</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.36902</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.36057</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.3484</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.34871</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.34839</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.34887</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.35053</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.32175</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.32524</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.33772</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.34133</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.34408</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.33862</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.33024</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.32376</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.31885</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.31803</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.30916</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.30902</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.31394</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.31069</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.30976</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.31113</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.31099</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.3121</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.30697</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.30697</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.3094</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.30624</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.30631</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.30697</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.30743</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.31046</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.31138</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.29112</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.27892</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.26556</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.18083</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.22564</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.23903</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.0182</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.0006400000000000001</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>-0.02086</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04938</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.12174</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>-0.00574</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03937</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.0494</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.01499</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.0402</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.03739</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04802</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04756000000000001</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02441</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.02687</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04943</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>0.11988</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.0494</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04941</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.04923</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.00028</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.30218</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04945</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.04919</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04941</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.02886</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04939</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04928</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.04096</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.18573</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.21669</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.25144</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.27996</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.27822</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.27993</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.27907</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.28383</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.30026</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.3182</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.30723</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.30868</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.29372</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.31179</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.31842</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.32262</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.31007</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.31981</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.30544</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.31948</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.31225</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.3424700000000001</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.42653</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.33817</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.34964</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.32547</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.31233</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.30964</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.30465</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.3097200000000001</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.33056</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.19924</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.67034</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.48701</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.23414</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.38957</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.33318</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.33242</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.33148</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.32502</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.33131</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.30948</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.30839</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.28139</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.27559</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.30028</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.28214</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.26099</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.29131</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.27055</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.31127</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.29422</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.30552</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.28122</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.32305</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.30913</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.34052</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.37984</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.33525</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.30142</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.30085</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.26365</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.2304</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.7222499999999999</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.7320599999999999</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.72211</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.67375</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.21068</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.33587</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.12584</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.25835</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.22298</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.17797</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.18024</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.14791</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.24181</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.16569</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.32766</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.07038</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.03038</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.11283</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.15305</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-0.04021</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.20689</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.01857</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.17566</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.1822</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.19205</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.0058</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.1585</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.16612</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.16565</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.19749</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25635</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29399</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.27691</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.3171</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.33006</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.33039</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.32638</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.33704</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.33291</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.33694</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.33018</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.35627</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.36431</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.37457</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.33974</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.38598</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.38066</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.42294</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.37509</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.37403</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.3636</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>0.36162</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.35337</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.36973</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.35553</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.3652</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.37444</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.33511</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.33162</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.32865</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.32961</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.32917</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.33737</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.32369</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33011</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.35615</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.365</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.33388</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.33747</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.33744</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.33214</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.33168</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.33465</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.32969</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.33956</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.3438</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.33936</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.32834</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.33941</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.09968</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.33418</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.32454</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.32046</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.32809</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.32812</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.33653</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.32888</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.33903</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.33982</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.5531</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.50848</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.4161</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.40814</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.33569</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.32249</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.33031</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.41438</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.41529</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.4102</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.43089</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.37095</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.42975</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.37071</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.36451</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.36411</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.44581</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.32967</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.31145</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.32729</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.33159</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.31195</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.14067</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.2766</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.27012</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.3053</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.32855</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.33318</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.32243</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.34046</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.29072</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.31107</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.31136</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.29161</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.31268</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.31934</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.32362</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.32931</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.35728</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.3321</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.35848</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.35095</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.35175</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.35331</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.35278</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.35986</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.33506</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.36127</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.3592</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.33636</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.35083</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.33995</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.36437</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.36921</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.324</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.42308</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.35862</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.39024</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.35849</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.37731</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.35113</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.36099</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.35149</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.3672</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.34469</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.31064</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.32747</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.32104</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.32669</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.32646</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.37841</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.3317</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.33165</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.29777</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.3168</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.32058</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.3417</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.32942</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.33108</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.3333</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.34538</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.34515</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.32481</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.34618</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.34017</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.33639</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.32107</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.32083</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.33089</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34646</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.33123</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.34022</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.35067</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.3233</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.36327</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.35526</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.36945</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.35937</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.35935</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.36357</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.33046</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.35342</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.34712</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.52691</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.326</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.50946</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.37425</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.48092</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.37659</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.36089</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.35731</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.35997</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.3098399999999999</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.35339</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.34607</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.43022</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.35886</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.31115</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.4808</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.38001</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.34089</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.26257</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.33944</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.34794</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.35108</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>1.32877</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.27799</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.28728</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.3395</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.85492</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>1.34724</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.84475</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.84317</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.8566699999999999</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>1.40749</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>1.4038</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>1.46279</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>1.46942</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>1.35742</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>1.56578</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>1.38134</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>1.36597</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>1.40018</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.85287</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.85562</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.84597</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.84734</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.85365</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.84788</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.8518</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.85002</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.8490700000000001</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.8547100000000001</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.8509099999999999</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>1.27703</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.84597</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.8909199999999999</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.8478300000000001</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.347</v>
+      </c>
+      <c r="C140" t="n">
+        <v>1.4807</v>
+      </c>
+      <c r="D140" t="n">
+        <v>1.58331</v>
+      </c>
+      <c r="E140" t="n">
+        <v>1.5833</v>
+      </c>
+      <c r="F140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G140" t="n">
+        <v>1.38055</v>
+      </c>
+      <c r="H140" t="n">
+        <v>1.35994</v>
+      </c>
+      <c r="I140" t="n">
+        <v>1.37513</v>
+      </c>
+      <c r="J140" t="n">
+        <v>1.37408</v>
+      </c>
+      <c r="K140" t="n">
+        <v>1.37843</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.84622</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.8460800000000001</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.3667</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.60014</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.60001</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.5999099999999999</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.84597</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.84597</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.8459800000000001</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.84597</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.84597</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.8460800000000001</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.84596</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.8461000000000001</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.8469500000000001</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.84756</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.84878</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.84781</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.8462499999999999</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.60012</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.60022</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.36555</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.35556</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.60433</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.39936</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.60634</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.38295</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.45928</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.40012</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.37363</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.31123</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.35835</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.32912</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.37053</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.27331</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.38348</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.41179</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.36457</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29419</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.31459</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.33318</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.33899</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.31819</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.32092</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.34077</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.35082</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.32125</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.34359</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.35816</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.35516</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.30872</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.35775</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.35707</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.39214</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.38404</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.39407</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.37219</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.39921</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.48825</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.4089</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.45234</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.43558</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.42999</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.48857</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.5501200000000001</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.5505800000000001</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.3949</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.45132</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.50729</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.48091</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.5102300000000001</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.4527</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.40101</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.50039</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.48809</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.31248</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.70056</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.5180900000000001</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.52777</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.38327</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.41684</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.38003</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.36564</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.37735</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.36021</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.36429</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.26568</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.36956</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.33511</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.36645</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.33806</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.33833</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.34422</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.32965</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.33664</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.34318</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.34017</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.33687</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.36077</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.33861</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.33901</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.34102</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.32093</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.32862</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.32401</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.32266</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.8454400000000001</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.8453099999999999</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.84524</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.84584</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.84616</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.84496</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.84638</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.8462499999999999</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.8465</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.31347</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.8467</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.84733</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.8469800000000001</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.85265</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.85798</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.8539800000000001</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.24427</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.8540599999999999</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.31825</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.85848</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.28106</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.17983</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.06901</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.39403</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.35959</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.8665700000000001</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.8647100000000001</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.21323</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.172</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.0056</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.31979</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.26325</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.16639</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.06177000000000001</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.05479</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.07393999999999999</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.17031</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.08159999999999999</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.0596</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.18088</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.15578</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.17609</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.28839</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.32209</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.30985</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.29689</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.38163</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.35419</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.36153</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.38277</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.35838</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.36812</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.26366</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.35439</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.36288</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.35326</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.31627</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.42552</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.42226</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.4367</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.38494</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.402</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.42122</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.38865</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.39835</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.41526</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.39462</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.37759</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.40818</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.37064</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.41175</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.37498</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.36903</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.35512</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.12215</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.35992</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.34074</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.78026</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.51025</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.51222</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.8570099999999999</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.5711799999999999</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.34522</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.38984</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.38603</v>
+      </c>
+      <c r="K142" t="n">
+        <v>1.38155</v>
+      </c>
+      <c r="L142" t="n">
+        <v>1.3565</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.84756</v>
+      </c>
+      <c r="N142" t="n">
+        <v>1.35132</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.84545</v>
+      </c>
+      <c r="P142" t="n">
+        <v>1.35666</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.84533</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.84689</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.84748</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.84697</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.35744</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.36404</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.8459099999999999</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.8459500000000001</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.84678</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.84535</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.8458600000000001</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.84796</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.84624</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>1.35583</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.85541</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.31283</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.32673</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.8473099999999999</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.85487</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.8585199999999999</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.8588</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.85791</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.27942</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.86034</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.28843</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.85115</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.84256</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.01333</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.84184</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.01079</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>1.03869</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.83751</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.0337</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>-0.00577</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>1.0187</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>1.0455</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>1.01722</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.8473099999999999</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.8400700000000001</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>1.16272</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>1.27794</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.8476</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>1.17107</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.27026</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.83838</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.43736</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.46031</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.43309</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.5245</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.4720299999999999</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.44135</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.35576</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.45093</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.48783</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.4504</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.42899</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.4302</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.4213</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.46535</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.46995</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.47972</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.52013</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.5486</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.49038</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.47532</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.47859</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.47793</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.48277</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.47371</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.86119</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.49089</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.45981</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.4719</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.5883700000000001</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.6652400000000001</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.36123</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.3643</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.35817</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.36356</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.36592</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.33621</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.54625</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.44355</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.4163</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.33239</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.36406</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.35846</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.36071</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.3511</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.44609</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.35003</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.39028</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.37592</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.35177</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.35037</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.35481</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.33287</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.34074</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.34756</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.33526</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.84587</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.84576</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.84558</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.8459800000000001</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.84597</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.8465499999999999</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.84585</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.8460599999999999</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.8460299999999999</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.31985</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.28872</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.84739</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.84681</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.14963</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.21725</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.24115</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.24549</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.11967</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.15872</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.02921</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>-0.01198</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.04715</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.04719</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.04558</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.04606</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.04407</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.04134</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.08159999999999999</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.02832</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.84573</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.10042</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.18025</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.20737</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.12642</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.27349</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.24228</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.1297</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.08447</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.84748</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>1.15537</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.84646</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.84845</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.8463999999999999</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.85046</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.84677</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.84714</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.84861</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.84799</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.84805</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.84784</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.40083</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.44055</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.46119</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.50546</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.5374800000000001</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.5093299999999999</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.48032</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.53973</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.538</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.8537</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.8517</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.8556</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.54483</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.85833</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.5447000000000001</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.5439700000000001</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.5444199999999999</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.54995</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.8622300000000001</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.5407999999999999</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.50837</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.47745</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.47686</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.45491</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.43046</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.37557</v>
       </c>
     </row>
   </sheetData>
